--- a/public/templates/import-kelas.xlsx
+++ b/public/templates/import-kelas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ekskulio\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70226C53-3B7A-4284-BBDB-067B7B964E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CF207F-1C94-4810-865D-5CEA04D70957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1728" windowWidth="21600" windowHeight="11232" xr2:uid="{CDC1ACF0-9087-4BBD-A3C1-E4B7A3B0C523}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CDC1ACF0-9087-4BBD-A3C1-E4B7A3B0C523}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -115,7 +115,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -123,11 +123,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -136,6 +151,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,14 +471,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865C1D33-BA53-4B78-BF39-5FAA9EC9879E}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" customWidth="1"/>
     <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -467,11 +489,12 @@
       <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
@@ -479,11 +502,12 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>3</v>
@@ -493,6 +517,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
